--- a/data_default.xlsx
+++ b/data_default.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22827"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B62ED1-8F8E-4788-A779-AC181BC39BF1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Agregat CKG" sheetId="1" r:id="rId1"/>
@@ -13,14 +14,463 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="148">
+  <si>
+    <t>Nama Provinsi</t>
+  </si>
+  <si>
+    <t>Nama Kabupaten Kota</t>
+  </si>
+  <si>
+    <t>Nama Kecamatan</t>
+  </si>
+  <si>
+    <t>Nama Faskes</t>
+  </si>
+  <si>
+    <t>Jumlah Peserta Hadir Usia 18 Tahun</t>
+  </si>
+  <si>
+    <t>Jumlah Orang Diperiksa Tekanan Darah</t>
+  </si>
+  <si>
+    <t>Jumlah Penderita Hipertensi</t>
+  </si>
+  <si>
+    <t>Diagnosis Hipertensi</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Diagnosis Hipertensi - Gejala Masih Belum Spesifik</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Diagnosis Hipertensi - Keterbatasan Fasilitas Pemeriksaan</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Diagnosis Hipertensi - Waktu Pemeriksaan Terbatas</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Diagnosis Hipertensi - Perlu Rujukan ke Fasilitas yang Lebih Lengkap</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Diagnosis Hipertensi - Perlu Pemeriksaan Penunjang Lainnya</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Diagnosis Hipertensi - Lainnya</t>
+  </si>
+  <si>
+    <t>Diberikan Obat</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Hipertensi - Obat Tidak Tersedia</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Hipertensi - Pasien Menolak Diberikan Obat</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Hipertensi - Riwayat Alergi atau Kontraindikasi Obat</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Hipertensi - Tidak Ada Indikasi Medis</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Hipertensi - Risiko Efek Samping Lebih Besar Daripada Manfaat</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Hipertensi - Tidak Masuk dalam Skema Pembiayaan Puskesmas</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Hipertensi - Lainnya</t>
+  </si>
+  <si>
+    <t>Edukasi Hipertensi</t>
+  </si>
+  <si>
+    <t>Rujuk Hipertensi</t>
+  </si>
+  <si>
+    <t>Rujuk Hipertensi Derajat 3</t>
+  </si>
+  <si>
+    <t>Jumlah Peserta hadir Usia ≥18 Tahun</t>
+  </si>
+  <si>
+    <t>Jumlah Orang Diperiksa gula darah (Usia ≥ 18 Tahun)</t>
+  </si>
+  <si>
+    <t>Jumlah Penderita Diabetes</t>
+  </si>
+  <si>
+    <t>Diberikan Diagnosis</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Diagnosis Diabetes - Gejala Masih Belum Spesifik</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Diagnosis Diabetes - Keterbatasan Fasilitas Pemeriksaan</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Diagnosis Diabetes - Waktu Pemeriksaan Terbatas</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Diagnosis Diabetes - Perlu Rujukan ke Fasilitas yang Lebih Lengkap</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Diagnosis Diabetes - Perlu Pemeriksaan Penunjang Lainnya</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Diagnosis Diabetes - Lainnya</t>
+  </si>
+  <si>
+    <t>Diberikan Obat Diabetes</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Diabetes - Obat Tidak Tersedia</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Diabetes - Pasien Menolak Diberikan Obat</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Diabetes - Riwayat Alergi Atau Kontraindikasi Obat</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Diabetes - Tidak Ada Indikasi Medis</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Diabetes - Risiko Efek Samping Lebih Besar Daripada Manfaat</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Diabetes - Tidak Masuk Dalam Skema Pembiayaan Puskesmas</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Diabetes - Lainnya</t>
+  </si>
+  <si>
+    <t>Edukasi Diabetes</t>
+  </si>
+  <si>
+    <t>Rujuk Diabetes</t>
+  </si>
+  <si>
+    <t>Jumlah Penderita Prediabetes ≥18 Tahun</t>
+  </si>
+  <si>
+    <t>Jumlah Penderita Prediabetes risiko tinggi* ≥18 Tahun</t>
+  </si>
+  <si>
+    <t>Jumlah Penderita Prediabetes risiko tinggi* yang didiagnosis</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Diagnosis Prediabetes - Gejala Masih Belum Spesifik</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Diagnosis Prediabetes - Keterbatasan Fasilitas Pemeriksaan</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Diagnosis Prediabetes - Waktu Pemeriksaan Terbatas</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Diagnosis Prediabetes - Perlu Rujukan ke Fasilitas yang Lebih Lengkap</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Diagnosis Prediabetes - Perlu Pemeriksaan Penunjang Lainnya</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Diagnosis Prediabetes - Lainnya</t>
+  </si>
+  <si>
+    <t>Jumlah Penderita Prediabetes risiko tinggi* yang diberikan Obat</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Prediabetes - Obat Tidak Tersedia</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Prediabetes - Pasien Menolak Diberikan Obat</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Prediabetes - Riwayat Alergi Atau Kontraindikasi Obat</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Prediabetes - Tidak Ada Indikasi Medis</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Prediabetes - Risiko Efek Samping Lebih Besar Daripada Manfaat</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Prediabetes - Tidak Masuk Dalam Skema Pembiayaan Puskesmas</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Prediabetes - Lainnya</t>
+  </si>
+  <si>
+    <t>Edukasi Prediabetes (semua)</t>
+  </si>
+  <si>
+    <t>Rujuk Prediabetes (semua)</t>
+  </si>
+  <si>
+    <t>Jumlah Peserta Usia 40 Tahun dengan  HT dan/atau DM</t>
+  </si>
+  <si>
+    <t>Jumlah Peserta Usia 40 Tahun dengan  HT dan/atau DM yang Diperiksa profil lipid</t>
+  </si>
+  <si>
+    <t>Jumlah Peserta Dislipidemia</t>
+  </si>
+  <si>
+    <t>Diagnosis Dislipidemia</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Diagnosis - Gejala Masih Belum Spesifik</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Diagnosis - Keterbatasan Fasilitas Pemeriksaan</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Diagnosis - Waktu Pemeriksaan Terbatas</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Diagnosis - Perlu Rujukan Ke Fasilitas Yang Lebih Lengkap</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Diagnosis - Perlu Pemeriksaan Penunjang Lainnya</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Diagnosis - Lainnya</t>
+  </si>
+  <si>
+    <t>Diberikan Obat dislipidemia</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Dislipidemia - Obat Tidak Tersedia</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Dislipidemia - Pasien Menolak Diberikan Obat</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Dislipidemia - Riwayat Alergi Atau Kontraindikasi Obat</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Dislipidemia - Tidak Ada Indikasi Medis</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Dislipidemia - Risiko Efek Samping Lebih Besar Daripada Manfaat</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Dislipidemia - Tidak Masuk Dalam Skema Pembiayaan Puskesmas</t>
+  </si>
+  <si>
+    <t>Alasan Tidak Diberikan Obat Dislipidemia - Lainnya</t>
+  </si>
+  <si>
+    <t>Edukasi Dislipidemia</t>
+  </si>
+  <si>
+    <t>Total Peserta hadir (semua umur)</t>
+  </si>
+  <si>
+    <t>Total Peserta Diperiksa karies gigi</t>
+  </si>
+  <si>
+    <t>Jumlah Peserta dengan Gigi Karies (semua umur =&gt;1 Tahun)</t>
+  </si>
+  <si>
+    <t>Tertatalaksana Gigi Karies (semua umur =&gt;1 Tahun)</t>
+  </si>
+  <si>
+    <t>Diagnosis Gigi Karies (semua umur =&gt;1 Tahun)</t>
+  </si>
+  <si>
+    <t>Tindakan Medis Gigi Karies (semua umur =&gt;1 Tahun)</t>
+  </si>
+  <si>
+    <t>Obat Gigi Karies (semua umur =&gt;1 Tahun)</t>
+  </si>
+  <si>
+    <t>Tindak Lanjut Gigi Karies (semua umur =&gt;1 Tahun)</t>
+  </si>
+  <si>
+    <t>Edukasi Gigi Karies (semua umur =&gt;1 Tahun)</t>
+  </si>
+  <si>
+    <t>Diagnosis dan Edukasi Gigi Karies (semua umur =&gt;1 Tahun)</t>
+  </si>
+  <si>
+    <t>Diagnosis Edukasi dan Tindakan Medis Gigi Karies (semua umur =&gt;1 Tahun)</t>
+  </si>
+  <si>
+    <t>Diagnosis Edukasi dan Obat Gigi Karies (semua umur =&gt;1 Tahun)</t>
+  </si>
+  <si>
+    <t>Diagnosis dan Edukasi dan Obat dan Tindakan Medis Gigi Karies (semua umur =&gt;1 Tahun)</t>
+  </si>
+  <si>
+    <t>Jumlah Peserta hadir Usia 6-12 Tahun</t>
+  </si>
+  <si>
+    <t>Total Peserta Diperiksa Gigi Karies (Usia 6-12 Tahun)</t>
+  </si>
+  <si>
+    <t>Jumlah Peserta tanpa Gigi Karies (Usia 6-12 Tahun)</t>
+  </si>
+  <si>
+    <t>Jumlah Peserta dengan Gigi Karies (Usia 6-12 Tahun)</t>
+  </si>
+  <si>
+    <t>Tertatalaksana Gigi Karies (Usia 6-12 Tahun)</t>
+  </si>
+  <si>
+    <t>Diagnosis Gigi Karies (Usia 6-12 Tahun)</t>
+  </si>
+  <si>
+    <t>Tindakan medis Gigi Karies (Usia 6-12 Tahun)</t>
+  </si>
+  <si>
+    <t>Tindakan medis 'pemberian fluoride' Gigi Karies (Usia 6-12 Tahun)</t>
+  </si>
+  <si>
+    <t>Edukasi Gigi Karies (Usia 6-12 Tahun)</t>
+  </si>
+  <si>
+    <t>Diberikan Obat Gigi Karies (Usia 6-12 Tahun)</t>
+  </si>
+  <si>
+    <t>Diagnosis dan Edukasi Gigi Karies (Usia 6-12 Tahun)</t>
+  </si>
+  <si>
+    <t>Diagnosis dan Edukasi dan Tindakan Medis Gigi Karies (Usia 6-12 Tahun)</t>
+  </si>
+  <si>
+    <t>Diagnosis dan Edukasi dan Obat Gigi Karies (Usia 6-12 Tahun)</t>
+  </si>
+  <si>
+    <t>Diagnosis dan Edukasi dan Obat dan Tindakan Medis Gigi Karies (Usia 6-12 Tahun)</t>
+  </si>
+  <si>
+    <t>Sulawesi Selatan</t>
+  </si>
+  <si>
+    <t>Kab. Pangkajene Kepulauan</t>
+  </si>
+  <si>
+    <t>Balocci</t>
+  </si>
+  <si>
+    <t>BALOCCI</t>
+  </si>
+  <si>
+    <t>Tondong Tallasa</t>
+  </si>
+  <si>
+    <t>BANTIMALA</t>
+  </si>
+  <si>
+    <t>Segeri</t>
+  </si>
+  <si>
+    <t>BARING</t>
+  </si>
+  <si>
+    <t>Pangkajene</t>
+  </si>
+  <si>
+    <t>BONTO PERAK</t>
+  </si>
+  <si>
+    <t>Bungoro</t>
+  </si>
+  <si>
+    <t>BOWONG CINDEA</t>
+  </si>
+  <si>
+    <t>BUNGORO</t>
+  </si>
+  <si>
+    <t>Minasate'ne</t>
+  </si>
+  <si>
+    <t>KALABBIRANG</t>
+  </si>
+  <si>
+    <t>KOTA PANGKAJENE</t>
+  </si>
+  <si>
+    <t>Labakkang</t>
+  </si>
+  <si>
+    <t>LABAKKANG</t>
+  </si>
+  <si>
+    <t>Liukang Kalmas</t>
+  </si>
+  <si>
+    <t>LIUKANG KALMAS</t>
+  </si>
+  <si>
+    <t>Liukang Tangaya</t>
+  </si>
+  <si>
+    <t>LIUKANG TANGAYA</t>
+  </si>
+  <si>
+    <t>Liukang Tupabbiring</t>
+  </si>
+  <si>
+    <t>LIUKANG TUPABBIRING</t>
+  </si>
+  <si>
+    <t>Mandalle</t>
+  </si>
+  <si>
+    <t>MANDALLE</t>
+  </si>
+  <si>
+    <t>Marang</t>
+  </si>
+  <si>
+    <t>MA'RANG</t>
+  </si>
+  <si>
+    <t>MINASATE'NE</t>
+  </si>
+  <si>
+    <t>PADANG LAMPE</t>
+  </si>
+  <si>
+    <t>PAMMANTAUANG</t>
+  </si>
+  <si>
+    <t>PUNDATA BAJI</t>
+  </si>
+  <si>
+    <t>Liukang Tupabbiring Utara</t>
+  </si>
+  <si>
+    <t>SABUTUNG</t>
+  </si>
+  <si>
+    <t>SAILUS</t>
+  </si>
+  <si>
+    <t>SARAPPO</t>
+  </si>
+  <si>
+    <t>SEGERI</t>
+  </si>
+  <si>
+    <t>TARAWEANG</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -50,12 +500,20 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -311,582 +769,354 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:DF24"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Nama Provinsi</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nama Kabupaten Kota</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Nama Kecamatan</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Nama Faskes</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Jumlah Peserta Hadir Usia 18 Tahun</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Jumlah Orang Diperiksa Tekanan Darah</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Jumlah Penderita Hipertensi</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Diagnosis Hipertensi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Diagnosis Hipertensi - Gejala Masih Belum Spesifik</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Diagnosis Hipertensi - Keterbatasan Fasilitas Pemeriksaan</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Diagnosis Hipertensi - Waktu Pemeriksaan Terbatas</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Diagnosis Hipertensi - Perlu Rujukan ke Fasilitas yang Lebih Lengkap</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Diagnosis Hipertensi - Perlu Pemeriksaan Penunjang Lainnya</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Diagnosis Hipertensi - Lainnya</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Diberikan Obat</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Hipertensi - Obat Tidak Tersedia</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Hipertensi - Pasien Menolak Diberikan Obat</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Hipertensi - Riwayat Alergi atau Kontraindikasi Obat</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Hipertensi - Tidak Ada Indikasi Medis</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Hipertensi - Risiko Efek Samping Lebih Besar Daripada Manfaat</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Hipertensi - Tidak Masuk dalam Skema Pembiayaan Puskesmas</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Hipertensi - Lainnya</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Edukasi Hipertensi</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Rujuk Hipertensi</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Rujuk Hipertensi Derajat 3</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Jumlah Peserta hadir Usia ≥18 Tahun</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Jumlah Orang Diperiksa gula darah (Usia ≥ 18 Tahun)</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Jumlah Penderita Diabetes</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>Diberikan Diagnosis</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Diagnosis Diabetes - Gejala Masih Belum Spesifik</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Diagnosis Diabetes - Keterbatasan Fasilitas Pemeriksaan</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Diagnosis Diabetes - Waktu Pemeriksaan Terbatas</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Diagnosis Diabetes - Perlu Rujukan ke Fasilitas yang Lebih Lengkap</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Diagnosis Diabetes - Perlu Pemeriksaan Penunjang Lainnya</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Diagnosis Diabetes - Lainnya</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Diberikan Obat Diabetes</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Diabetes - Obat Tidak Tersedia</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Diabetes - Pasien Menolak Diberikan Obat</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Diabetes - Riwayat Alergi Atau Kontraindikasi Obat</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Diabetes - Tidak Ada Indikasi Medis</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Diabetes - Risiko Efek Samping Lebih Besar Daripada Manfaat</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Diabetes - Tidak Masuk Dalam Skema Pembiayaan Puskesmas</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Diabetes - Lainnya</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>Edukasi Diabetes</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>Rujuk Diabetes</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>Jumlah Penderita Prediabetes ≥18 Tahun</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>Jumlah Penderita Prediabetes risiko tinggi* ≥18 Tahun</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>Jumlah Penderita Prediabetes risiko tinggi* yang didiagnosis</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Diagnosis Prediabetes - Gejala Masih Belum Spesifik</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Diagnosis Prediabetes - Keterbatasan Fasilitas Pemeriksaan</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Diagnosis Prediabetes - Waktu Pemeriksaan Terbatas</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Diagnosis Prediabetes - Perlu Rujukan ke Fasilitas yang Lebih Lengkap</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Diagnosis Prediabetes - Perlu Pemeriksaan Penunjang Lainnya</t>
-        </is>
-      </c>
-      <c r="BB1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Diagnosis Prediabetes - Lainnya</t>
-        </is>
-      </c>
-      <c r="BC1" t="inlineStr">
-        <is>
-          <t>Jumlah Penderita Prediabetes risiko tinggi* yang diberikan Obat</t>
-        </is>
-      </c>
-      <c r="BD1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Prediabetes - Obat Tidak Tersedia</t>
-        </is>
-      </c>
-      <c r="BE1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Prediabetes - Pasien Menolak Diberikan Obat</t>
-        </is>
-      </c>
-      <c r="BF1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Prediabetes - Riwayat Alergi Atau Kontraindikasi Obat</t>
-        </is>
-      </c>
-      <c r="BG1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Prediabetes - Tidak Ada Indikasi Medis</t>
-        </is>
-      </c>
-      <c r="BH1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Prediabetes - Risiko Efek Samping Lebih Besar Daripada Manfaat</t>
-        </is>
-      </c>
-      <c r="BI1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Prediabetes - Tidak Masuk Dalam Skema Pembiayaan Puskesmas</t>
-        </is>
-      </c>
-      <c r="BJ1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Prediabetes - Lainnya</t>
-        </is>
-      </c>
-      <c r="BK1" t="inlineStr">
-        <is>
-          <t>Edukasi Prediabetes (semua)</t>
-        </is>
-      </c>
-      <c r="BL1" t="inlineStr">
-        <is>
-          <t>Rujuk Prediabetes (semua)</t>
-        </is>
-      </c>
-      <c r="BM1" t="inlineStr">
-        <is>
-          <t>Jumlah Peserta Usia 40 Tahun dengan  HT dan/atau DM</t>
-        </is>
-      </c>
-      <c r="BN1" t="inlineStr">
-        <is>
-          <t>Jumlah Peserta Usia 40 Tahun dengan  HT dan/atau DM yang Diperiksa profil lipid</t>
-        </is>
-      </c>
-      <c r="BO1" t="inlineStr">
-        <is>
-          <t>Jumlah Peserta Dislipidemia</t>
-        </is>
-      </c>
-      <c r="BP1" t="inlineStr">
-        <is>
-          <t>Diagnosis Dislipidemia</t>
-        </is>
-      </c>
-      <c r="BQ1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Diagnosis - Gejala Masih Belum Spesifik</t>
-        </is>
-      </c>
-      <c r="BR1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Diagnosis - Keterbatasan Fasilitas Pemeriksaan</t>
-        </is>
-      </c>
-      <c r="BS1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Diagnosis - Waktu Pemeriksaan Terbatas</t>
-        </is>
-      </c>
-      <c r="BT1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Diagnosis - Perlu Rujukan Ke Fasilitas Yang Lebih Lengkap</t>
-        </is>
-      </c>
-      <c r="BU1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Diagnosis - Perlu Pemeriksaan Penunjang Lainnya</t>
-        </is>
-      </c>
-      <c r="BV1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Diagnosis - Lainnya</t>
-        </is>
-      </c>
-      <c r="BW1" t="inlineStr">
-        <is>
-          <t>Diberikan Obat dislipidemia</t>
-        </is>
-      </c>
-      <c r="BX1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Dislipidemia - Obat Tidak Tersedia</t>
-        </is>
-      </c>
-      <c r="BY1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Dislipidemia - Pasien Menolak Diberikan Obat</t>
-        </is>
-      </c>
-      <c r="BZ1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Dislipidemia - Riwayat Alergi Atau Kontraindikasi Obat</t>
-        </is>
-      </c>
-      <c r="CA1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Dislipidemia - Tidak Ada Indikasi Medis</t>
-        </is>
-      </c>
-      <c r="CB1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Dislipidemia - Risiko Efek Samping Lebih Besar Daripada Manfaat</t>
-        </is>
-      </c>
-      <c r="CC1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Dislipidemia - Tidak Masuk Dalam Skema Pembiayaan Puskesmas</t>
-        </is>
-      </c>
-      <c r="CD1" t="inlineStr">
-        <is>
-          <t>Alasan Tidak Diberikan Obat Dislipidemia - Lainnya</t>
-        </is>
-      </c>
-      <c r="CE1" t="inlineStr">
-        <is>
-          <t>Edukasi Dislipidemia</t>
-        </is>
-      </c>
-      <c r="CF1" t="inlineStr">
-        <is>
-          <t>Total Peserta hadir (semua umur)</t>
-        </is>
-      </c>
-      <c r="CG1" t="inlineStr">
-        <is>
-          <t>Total Peserta Diperiksa karies gigi</t>
-        </is>
-      </c>
-      <c r="CH1" t="inlineStr">
-        <is>
-          <t>Jumlah Peserta dengan Gigi Karies (semua umur =&gt;1 Tahun)</t>
-        </is>
-      </c>
-      <c r="CI1" t="inlineStr">
-        <is>
-          <t>Tertatalaksana Gigi Karies (semua umur =&gt;1 Tahun)</t>
-        </is>
-      </c>
-      <c r="CJ1" t="inlineStr">
-        <is>
-          <t>Diagnosis Gigi Karies (semua umur =&gt;1 Tahun)</t>
-        </is>
-      </c>
-      <c r="CK1" t="inlineStr">
-        <is>
-          <t>Tindakan Medis Gigi Karies (semua umur =&gt;1 Tahun)</t>
-        </is>
-      </c>
-      <c r="CL1" t="inlineStr">
-        <is>
-          <t>Obat Gigi Karies (semua umur =&gt;1 Tahun)</t>
-        </is>
-      </c>
-      <c r="CM1" t="inlineStr">
-        <is>
-          <t>Tindak Lanjut Gigi Karies (semua umur =&gt;1 Tahun)</t>
-        </is>
-      </c>
-      <c r="CN1" t="inlineStr">
-        <is>
-          <t>Edukasi Gigi Karies (semua umur =&gt;1 Tahun)</t>
-        </is>
-      </c>
-      <c r="CO1" t="inlineStr">
-        <is>
-          <t>Diagnosis dan Edukasi Gigi Karies (semua umur =&gt;1 Tahun)</t>
-        </is>
-      </c>
-      <c r="CP1" t="inlineStr">
-        <is>
-          <t>Diagnosis Edukasi dan Tindakan Medis Gigi Karies (semua umur =&gt;1 Tahun)</t>
-        </is>
-      </c>
-      <c r="CQ1" t="inlineStr">
-        <is>
-          <t>Diagnosis Edukasi dan Obat Gigi Karies (semua umur =&gt;1 Tahun)</t>
-        </is>
-      </c>
-      <c r="CR1" t="inlineStr">
-        <is>
-          <t>Diagnosis dan Edukasi dan Obat dan Tindakan Medis Gigi Karies (semua umur =&gt;1 Tahun)</t>
-        </is>
-      </c>
-      <c r="CS1" t="inlineStr">
-        <is>
-          <t>Jumlah Peserta hadir Usia 6-12 Tahun</t>
-        </is>
-      </c>
-      <c r="CT1" t="inlineStr">
-        <is>
-          <t>Total Peserta Diperiksa Gigi Karies (Usia 6-12 Tahun)</t>
-        </is>
-      </c>
-      <c r="CU1" t="inlineStr">
-        <is>
-          <t>Jumlah Peserta tanpa Gigi Karies (Usia 6-12 Tahun)</t>
-        </is>
-      </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>Jumlah Peserta dengan Gigi Karies (Usia 6-12 Tahun)</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>Tertatalaksana Gigi Karies (Usia 6-12 Tahun)</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>Diagnosis Gigi Karies (Usia 6-12 Tahun)</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>Tindakan medis Gigi Karies (Usia 6-12 Tahun)</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>Tindakan medis 'pemberian fluoride' Gigi Karies (Usia 6-12 Tahun)</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>Edukasi Gigi Karies (Usia 6-12 Tahun)</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>Diberikan Obat Gigi Karies (Usia 6-12 Tahun)</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>Diagnosis dan Edukasi Gigi Karies (Usia 6-12 Tahun)</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>Diagnosis dan Edukasi dan Tindakan Medis Gigi Karies (Usia 6-12 Tahun)</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>Diagnosis dan Edukasi dan Obat Gigi Karies (Usia 6-12 Tahun)</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>Diagnosis dan Edukasi dan Obat dan Tindakan Medis Gigi Karies (Usia 6-12 Tahun)</t>
-        </is>
+    <row r="1" spans="1:110" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>74</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>75</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>76</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>77</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>78</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>79</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>80</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>81</v>
+      </c>
+      <c r="CE1" t="s">
+        <v>82</v>
+      </c>
+      <c r="CF1" t="s">
+        <v>83</v>
+      </c>
+      <c r="CG1" t="s">
+        <v>84</v>
+      </c>
+      <c r="CH1" t="s">
+        <v>85</v>
+      </c>
+      <c r="CI1" t="s">
+        <v>86</v>
+      </c>
+      <c r="CJ1" t="s">
+        <v>87</v>
+      </c>
+      <c r="CK1" t="s">
+        <v>88</v>
+      </c>
+      <c r="CL1" t="s">
+        <v>89</v>
+      </c>
+      <c r="CM1" t="s">
+        <v>90</v>
+      </c>
+      <c r="CN1" t="s">
+        <v>91</v>
+      </c>
+      <c r="CO1" t="s">
+        <v>92</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>93</v>
+      </c>
+      <c r="CQ1" t="s">
+        <v>94</v>
+      </c>
+      <c r="CR1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CS1" t="s">
+        <v>96</v>
+      </c>
+      <c r="CT1" t="s">
+        <v>97</v>
+      </c>
+      <c r="CU1" t="s">
+        <v>98</v>
+      </c>
+      <c r="CV1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CW1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CX1" t="s">
+        <v>101</v>
+      </c>
+      <c r="CY1" t="s">
+        <v>102</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>103</v>
+      </c>
+      <c r="DA1" t="s">
+        <v>104</v>
+      </c>
+      <c r="DB1" t="s">
+        <v>105</v>
+      </c>
+      <c r="DC1" t="s">
+        <v>106</v>
+      </c>
+      <c r="DD1" t="s">
+        <v>107</v>
+      </c>
+      <c r="DE1" t="s">
+        <v>108</v>
+      </c>
+      <c r="DF1" t="s">
+        <v>109</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Sulawesi Selatan</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Kab. Pangkajene Kepulauan</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Balocci</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>BALOCCI</t>
-        </is>
+    <row r="2" spans="1:110" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" t="s">
+        <v>113</v>
       </c>
       <c r="E2">
         <v>1427</v>
@@ -1207,26 +1437,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Sulawesi Selatan</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Kab. Pangkajene Kepulauan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Tondong Tallasa</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>BANTIMALA</t>
-        </is>
+    <row r="3" spans="1:110" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" t="s">
+        <v>115</v>
       </c>
       <c r="E3">
         <v>7071</v>
@@ -1547,26 +1769,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Sulawesi Selatan</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Kab. Pangkajene Kepulauan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Segeri</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>BARING</t>
-        </is>
+    <row r="4" spans="1:110" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" t="s">
+        <v>117</v>
       </c>
       <c r="E4">
         <v>4783</v>
@@ -1887,26 +2101,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Sulawesi Selatan</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Kab. Pangkajene Kepulauan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Pangkajene</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>BONTO PERAK</t>
-        </is>
+    <row r="5" spans="1:110" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" t="s">
+        <v>119</v>
       </c>
       <c r="E5">
         <v>13154</v>
@@ -2227,26 +2433,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Sulawesi Selatan</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kab. Pangkajene Kepulauan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bungoro</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>BOWONG CINDEA</t>
-        </is>
+    <row r="6" spans="1:110" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D6" t="s">
+        <v>121</v>
       </c>
       <c r="E6">
         <v>9787</v>
@@ -2567,26 +2765,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Sulawesi Selatan</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Kab. Pangkajene Kepulauan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bungoro</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>BUNGORO</t>
-        </is>
+    <row r="7" spans="1:110" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D7" t="s">
+        <v>122</v>
       </c>
       <c r="E7">
         <v>19342</v>
@@ -2907,26 +3097,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Sulawesi Selatan</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Kab. Pangkajene Kepulauan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Minasate'ne</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>KALABBIRANG</t>
-        </is>
+    <row r="8" spans="1:110" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" t="s">
+        <v>124</v>
       </c>
       <c r="E8">
         <v>5410</v>
@@ -3247,26 +3429,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Sulawesi Selatan</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Kab. Pangkajene Kepulauan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Pangkajene</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>KOTA PANGKAJENE</t>
-        </is>
+    <row r="9" spans="1:110" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" t="s">
+        <v>125</v>
       </c>
       <c r="E9">
         <v>21299</v>
@@ -3587,26 +3761,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sulawesi Selatan</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Kab. Pangkajene Kepulauan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Labakkang</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LABAKKANG</t>
-        </is>
+    <row r="10" spans="1:110" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D10" t="s">
+        <v>127</v>
       </c>
       <c r="E10">
         <v>11021</v>
@@ -3927,26 +4093,18 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sulawesi Selatan</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Kab. Pangkajene Kepulauan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Liukang Kalmas</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LIUKANG KALMAS</t>
-        </is>
+    <row r="11" spans="1:110" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D11" t="s">
+        <v>129</v>
       </c>
       <c r="E11">
         <v>2837</v>
@@ -4267,26 +4425,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sulawesi Selatan</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Kab. Pangkajene Kepulauan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Liukang Tangaya</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LIUKANG TANGAYA</t>
-        </is>
+    <row r="12" spans="1:110" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" t="s">
+        <v>131</v>
       </c>
       <c r="E12">
         <v>6783</v>
@@ -4607,26 +4757,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Sulawesi Selatan</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Kab. Pangkajene Kepulauan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Liukang Tupabbiring</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>LIUKANG TUPABBIRING</t>
-        </is>
+    <row r="13" spans="1:110" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" t="s">
+        <v>132</v>
+      </c>
+      <c r="D13" t="s">
+        <v>133</v>
       </c>
       <c r="E13">
         <v>4095</v>
@@ -4947,26 +5089,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Sulawesi Selatan</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Kab. Pangkajene Kepulauan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Mandalle</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>MANDALLE</t>
-        </is>
+    <row r="14" spans="1:110" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D14" t="s">
+        <v>135</v>
       </c>
       <c r="E14">
         <v>9232</v>
@@ -5287,26 +5421,18 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Sulawesi Selatan</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Kab. Pangkajene Kepulauan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Marang</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>MA'RANG</t>
-        </is>
+    <row r="15" spans="1:110" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>110</v>
+      </c>
+      <c r="B15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" t="s">
+        <v>136</v>
+      </c>
+      <c r="D15" t="s">
+        <v>137</v>
       </c>
       <c r="E15">
         <v>17978</v>
@@ -5627,26 +5753,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Sulawesi Selatan</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Kab. Pangkajene Kepulauan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Minasate'ne</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>MINASATE'NE</t>
-        </is>
+    <row r="16" spans="1:110" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>110</v>
+      </c>
+      <c r="B16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D16" t="s">
+        <v>138</v>
       </c>
       <c r="E16">
         <v>13145</v>
@@ -5967,26 +6085,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Sulawesi Selatan</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Kab. Pangkajene Kepulauan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Marang</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>PADANG LAMPE</t>
-        </is>
+    <row r="17" spans="1:110" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>110</v>
+      </c>
+      <c r="B17" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" t="s">
+        <v>136</v>
+      </c>
+      <c r="D17" t="s">
+        <v>139</v>
       </c>
       <c r="E17">
         <v>6001</v>
@@ -6307,26 +6417,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Sulawesi Selatan</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Kab. Pangkajene Kepulauan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Liukang Kalmas</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>PAMMANTAUANG</t>
-        </is>
+    <row r="18" spans="1:110" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" t="s">
+        <v>128</v>
+      </c>
+      <c r="D18" t="s">
+        <v>140</v>
       </c>
       <c r="E18">
         <v>3502</v>
@@ -6647,26 +6749,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Sulawesi Selatan</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Kab. Pangkajene Kepulauan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Labakkang</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>PUNDATA BAJI</t>
-        </is>
+    <row r="19" spans="1:110" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D19" t="s">
+        <v>141</v>
       </c>
       <c r="E19">
         <v>9703</v>
@@ -6987,26 +7081,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Sulawesi Selatan</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Kab. Pangkajene Kepulauan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Liukang Tupabbiring Utara</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>SABUTUNG</t>
-        </is>
+    <row r="20" spans="1:110" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" t="s">
+        <v>142</v>
+      </c>
+      <c r="D20" t="s">
+        <v>143</v>
       </c>
       <c r="E20">
         <v>8451</v>
@@ -7327,26 +7413,18 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sulawesi Selatan</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Kab. Pangkajene Kepulauan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Liukang Tangaya</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>SAILUS</t>
-        </is>
+    <row r="21" spans="1:110" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" t="s">
+        <v>130</v>
+      </c>
+      <c r="D21" t="s">
+        <v>144</v>
       </c>
       <c r="E21">
         <v>4401</v>
@@ -7667,26 +7745,18 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Sulawesi Selatan</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Kab. Pangkajene Kepulauan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Liukang Tupabbiring</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>SARAPPO</t>
-        </is>
+    <row r="22" spans="1:110" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>110</v>
+      </c>
+      <c r="B22" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" t="s">
+        <v>145</v>
       </c>
       <c r="E22">
         <v>7323</v>
@@ -8007,26 +8077,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Sulawesi Selatan</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Kab. Pangkajene Kepulauan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Segeri</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>SEGERI</t>
-        </is>
+    <row r="23" spans="1:110" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>110</v>
+      </c>
+      <c r="B23" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" t="s">
+        <v>146</v>
       </c>
       <c r="E23">
         <v>10243</v>
@@ -8347,26 +8409,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Sulawesi Selatan</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Kab. Pangkajene Kepulauan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Labakkang</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>TARAWEANG</t>
-        </is>
+    <row r="24" spans="1:110" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" t="s">
+        <v>126</v>
+      </c>
+      <c r="D24" t="s">
+        <v>147</v>
       </c>
       <c r="E24">
         <v>8832</v>
@@ -8688,5 +8742,6 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data_default.xlsx
+++ b/data_default.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22827"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B62ED1-8F8E-4788-A779-AC181BC39BF1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Data Agregat CKG" sheetId="1" r:id="rId1"/>
@@ -14,463 +13,14 @@
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="148">
-  <si>
-    <t>Nama Provinsi</t>
-  </si>
-  <si>
-    <t>Nama Kabupaten Kota</t>
-  </si>
-  <si>
-    <t>Nama Kecamatan</t>
-  </si>
-  <si>
-    <t>Nama Faskes</t>
-  </si>
-  <si>
-    <t>Jumlah Peserta Hadir Usia 18 Tahun</t>
-  </si>
-  <si>
-    <t>Jumlah Orang Diperiksa Tekanan Darah</t>
-  </si>
-  <si>
-    <t>Jumlah Penderita Hipertensi</t>
-  </si>
-  <si>
-    <t>Diagnosis Hipertensi</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Diagnosis Hipertensi - Gejala Masih Belum Spesifik</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Diagnosis Hipertensi - Keterbatasan Fasilitas Pemeriksaan</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Diagnosis Hipertensi - Waktu Pemeriksaan Terbatas</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Diagnosis Hipertensi - Perlu Rujukan ke Fasilitas yang Lebih Lengkap</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Diagnosis Hipertensi - Perlu Pemeriksaan Penunjang Lainnya</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Diagnosis Hipertensi - Lainnya</t>
-  </si>
-  <si>
-    <t>Diberikan Obat</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Hipertensi - Obat Tidak Tersedia</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Hipertensi - Pasien Menolak Diberikan Obat</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Hipertensi - Riwayat Alergi atau Kontraindikasi Obat</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Hipertensi - Tidak Ada Indikasi Medis</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Hipertensi - Risiko Efek Samping Lebih Besar Daripada Manfaat</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Hipertensi - Tidak Masuk dalam Skema Pembiayaan Puskesmas</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Hipertensi - Lainnya</t>
-  </si>
-  <si>
-    <t>Edukasi Hipertensi</t>
-  </si>
-  <si>
-    <t>Rujuk Hipertensi</t>
-  </si>
-  <si>
-    <t>Rujuk Hipertensi Derajat 3</t>
-  </si>
-  <si>
-    <t>Jumlah Peserta hadir Usia ≥18 Tahun</t>
-  </si>
-  <si>
-    <t>Jumlah Orang Diperiksa gula darah (Usia ≥ 18 Tahun)</t>
-  </si>
-  <si>
-    <t>Jumlah Penderita Diabetes</t>
-  </si>
-  <si>
-    <t>Diberikan Diagnosis</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Diagnosis Diabetes - Gejala Masih Belum Spesifik</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Diagnosis Diabetes - Keterbatasan Fasilitas Pemeriksaan</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Diagnosis Diabetes - Waktu Pemeriksaan Terbatas</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Diagnosis Diabetes - Perlu Rujukan ke Fasilitas yang Lebih Lengkap</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Diagnosis Diabetes - Perlu Pemeriksaan Penunjang Lainnya</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Diagnosis Diabetes - Lainnya</t>
-  </si>
-  <si>
-    <t>Diberikan Obat Diabetes</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Diabetes - Obat Tidak Tersedia</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Diabetes - Pasien Menolak Diberikan Obat</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Diabetes - Riwayat Alergi Atau Kontraindikasi Obat</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Diabetes - Tidak Ada Indikasi Medis</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Diabetes - Risiko Efek Samping Lebih Besar Daripada Manfaat</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Diabetes - Tidak Masuk Dalam Skema Pembiayaan Puskesmas</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Diabetes - Lainnya</t>
-  </si>
-  <si>
-    <t>Edukasi Diabetes</t>
-  </si>
-  <si>
-    <t>Rujuk Diabetes</t>
-  </si>
-  <si>
-    <t>Jumlah Penderita Prediabetes ≥18 Tahun</t>
-  </si>
-  <si>
-    <t>Jumlah Penderita Prediabetes risiko tinggi* ≥18 Tahun</t>
-  </si>
-  <si>
-    <t>Jumlah Penderita Prediabetes risiko tinggi* yang didiagnosis</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Diagnosis Prediabetes - Gejala Masih Belum Spesifik</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Diagnosis Prediabetes - Keterbatasan Fasilitas Pemeriksaan</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Diagnosis Prediabetes - Waktu Pemeriksaan Terbatas</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Diagnosis Prediabetes - Perlu Rujukan ke Fasilitas yang Lebih Lengkap</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Diagnosis Prediabetes - Perlu Pemeriksaan Penunjang Lainnya</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Diagnosis Prediabetes - Lainnya</t>
-  </si>
-  <si>
-    <t>Jumlah Penderita Prediabetes risiko tinggi* yang diberikan Obat</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Prediabetes - Obat Tidak Tersedia</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Prediabetes - Pasien Menolak Diberikan Obat</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Prediabetes - Riwayat Alergi Atau Kontraindikasi Obat</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Prediabetes - Tidak Ada Indikasi Medis</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Prediabetes - Risiko Efek Samping Lebih Besar Daripada Manfaat</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Prediabetes - Tidak Masuk Dalam Skema Pembiayaan Puskesmas</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Prediabetes - Lainnya</t>
-  </si>
-  <si>
-    <t>Edukasi Prediabetes (semua)</t>
-  </si>
-  <si>
-    <t>Rujuk Prediabetes (semua)</t>
-  </si>
-  <si>
-    <t>Jumlah Peserta Usia 40 Tahun dengan  HT dan/atau DM</t>
-  </si>
-  <si>
-    <t>Jumlah Peserta Usia 40 Tahun dengan  HT dan/atau DM yang Diperiksa profil lipid</t>
-  </si>
-  <si>
-    <t>Jumlah Peserta Dislipidemia</t>
-  </si>
-  <si>
-    <t>Diagnosis Dislipidemia</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Diagnosis - Gejala Masih Belum Spesifik</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Diagnosis - Keterbatasan Fasilitas Pemeriksaan</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Diagnosis - Waktu Pemeriksaan Terbatas</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Diagnosis - Perlu Rujukan Ke Fasilitas Yang Lebih Lengkap</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Diagnosis - Perlu Pemeriksaan Penunjang Lainnya</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Diagnosis - Lainnya</t>
-  </si>
-  <si>
-    <t>Diberikan Obat dislipidemia</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Dislipidemia - Obat Tidak Tersedia</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Dislipidemia - Pasien Menolak Diberikan Obat</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Dislipidemia - Riwayat Alergi Atau Kontraindikasi Obat</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Dislipidemia - Tidak Ada Indikasi Medis</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Dislipidemia - Risiko Efek Samping Lebih Besar Daripada Manfaat</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Dislipidemia - Tidak Masuk Dalam Skema Pembiayaan Puskesmas</t>
-  </si>
-  <si>
-    <t>Alasan Tidak Diberikan Obat Dislipidemia - Lainnya</t>
-  </si>
-  <si>
-    <t>Edukasi Dislipidemia</t>
-  </si>
-  <si>
-    <t>Total Peserta hadir (semua umur)</t>
-  </si>
-  <si>
-    <t>Total Peserta Diperiksa karies gigi</t>
-  </si>
-  <si>
-    <t>Jumlah Peserta dengan Gigi Karies (semua umur =&gt;1 Tahun)</t>
-  </si>
-  <si>
-    <t>Tertatalaksana Gigi Karies (semua umur =&gt;1 Tahun)</t>
-  </si>
-  <si>
-    <t>Diagnosis Gigi Karies (semua umur =&gt;1 Tahun)</t>
-  </si>
-  <si>
-    <t>Tindakan Medis Gigi Karies (semua umur =&gt;1 Tahun)</t>
-  </si>
-  <si>
-    <t>Obat Gigi Karies (semua umur =&gt;1 Tahun)</t>
-  </si>
-  <si>
-    <t>Tindak Lanjut Gigi Karies (semua umur =&gt;1 Tahun)</t>
-  </si>
-  <si>
-    <t>Edukasi Gigi Karies (semua umur =&gt;1 Tahun)</t>
-  </si>
-  <si>
-    <t>Diagnosis dan Edukasi Gigi Karies (semua umur =&gt;1 Tahun)</t>
-  </si>
-  <si>
-    <t>Diagnosis Edukasi dan Tindakan Medis Gigi Karies (semua umur =&gt;1 Tahun)</t>
-  </si>
-  <si>
-    <t>Diagnosis Edukasi dan Obat Gigi Karies (semua umur =&gt;1 Tahun)</t>
-  </si>
-  <si>
-    <t>Diagnosis dan Edukasi dan Obat dan Tindakan Medis Gigi Karies (semua umur =&gt;1 Tahun)</t>
-  </si>
-  <si>
-    <t>Jumlah Peserta hadir Usia 6-12 Tahun</t>
-  </si>
-  <si>
-    <t>Total Peserta Diperiksa Gigi Karies (Usia 6-12 Tahun)</t>
-  </si>
-  <si>
-    <t>Jumlah Peserta tanpa Gigi Karies (Usia 6-12 Tahun)</t>
-  </si>
-  <si>
-    <t>Jumlah Peserta dengan Gigi Karies (Usia 6-12 Tahun)</t>
-  </si>
-  <si>
-    <t>Tertatalaksana Gigi Karies (Usia 6-12 Tahun)</t>
-  </si>
-  <si>
-    <t>Diagnosis Gigi Karies (Usia 6-12 Tahun)</t>
-  </si>
-  <si>
-    <t>Tindakan medis Gigi Karies (Usia 6-12 Tahun)</t>
-  </si>
-  <si>
-    <t>Tindakan medis 'pemberian fluoride' Gigi Karies (Usia 6-12 Tahun)</t>
-  </si>
-  <si>
-    <t>Edukasi Gigi Karies (Usia 6-12 Tahun)</t>
-  </si>
-  <si>
-    <t>Diberikan Obat Gigi Karies (Usia 6-12 Tahun)</t>
-  </si>
-  <si>
-    <t>Diagnosis dan Edukasi Gigi Karies (Usia 6-12 Tahun)</t>
-  </si>
-  <si>
-    <t>Diagnosis dan Edukasi dan Tindakan Medis Gigi Karies (Usia 6-12 Tahun)</t>
-  </si>
-  <si>
-    <t>Diagnosis dan Edukasi dan Obat Gigi Karies (Usia 6-12 Tahun)</t>
-  </si>
-  <si>
-    <t>Diagnosis dan Edukasi dan Obat dan Tindakan Medis Gigi Karies (Usia 6-12 Tahun)</t>
-  </si>
-  <si>
-    <t>Sulawesi Selatan</t>
-  </si>
-  <si>
-    <t>Kab. Pangkajene Kepulauan</t>
-  </si>
-  <si>
-    <t>Balocci</t>
-  </si>
-  <si>
-    <t>BALOCCI</t>
-  </si>
-  <si>
-    <t>Tondong Tallasa</t>
-  </si>
-  <si>
-    <t>BANTIMALA</t>
-  </si>
-  <si>
-    <t>Segeri</t>
-  </si>
-  <si>
-    <t>BARING</t>
-  </si>
-  <si>
-    <t>Pangkajene</t>
-  </si>
-  <si>
-    <t>BONTO PERAK</t>
-  </si>
-  <si>
-    <t>Bungoro</t>
-  </si>
-  <si>
-    <t>BOWONG CINDEA</t>
-  </si>
-  <si>
-    <t>BUNGORO</t>
-  </si>
-  <si>
-    <t>Minasate'ne</t>
-  </si>
-  <si>
-    <t>KALABBIRANG</t>
-  </si>
-  <si>
-    <t>KOTA PANGKAJENE</t>
-  </si>
-  <si>
-    <t>Labakkang</t>
-  </si>
-  <si>
-    <t>LABAKKANG</t>
-  </si>
-  <si>
-    <t>Liukang Kalmas</t>
-  </si>
-  <si>
-    <t>LIUKANG KALMAS</t>
-  </si>
-  <si>
-    <t>Liukang Tangaya</t>
-  </si>
-  <si>
-    <t>LIUKANG TANGAYA</t>
-  </si>
-  <si>
-    <t>Liukang Tupabbiring</t>
-  </si>
-  <si>
-    <t>LIUKANG TUPABBIRING</t>
-  </si>
-  <si>
-    <t>Mandalle</t>
-  </si>
-  <si>
-    <t>MANDALLE</t>
-  </si>
-  <si>
-    <t>Marang</t>
-  </si>
-  <si>
-    <t>MA'RANG</t>
-  </si>
-  <si>
-    <t>MINASATE'NE</t>
-  </si>
-  <si>
-    <t>PADANG LAMPE</t>
-  </si>
-  <si>
-    <t>PAMMANTAUANG</t>
-  </si>
-  <si>
-    <t>PUNDATA BAJI</t>
-  </si>
-  <si>
-    <t>Liukang Tupabbiring Utara</t>
-  </si>
-  <si>
-    <t>SABUTUNG</t>
-  </si>
-  <si>
-    <t>SAILUS</t>
-  </si>
-  <si>
-    <t>SARAPPO</t>
-  </si>
-  <si>
-    <t>SEGERI</t>
-  </si>
-  <si>
-    <t>TARAWEANG</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -500,20 +50,12 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -769,354 +311,582 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DF24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:110" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" t="s">
-        <v>55</v>
-      </c>
-      <c r="BE1" t="s">
-        <v>56</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>57</v>
-      </c>
-      <c r="BG1" t="s">
-        <v>58</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>59</v>
-      </c>
-      <c r="BI1" t="s">
-        <v>60</v>
-      </c>
-      <c r="BJ1" t="s">
-        <v>61</v>
-      </c>
-      <c r="BK1" t="s">
-        <v>62</v>
-      </c>
-      <c r="BL1" t="s">
-        <v>63</v>
-      </c>
-      <c r="BM1" t="s">
-        <v>64</v>
-      </c>
-      <c r="BN1" t="s">
-        <v>65</v>
-      </c>
-      <c r="BO1" t="s">
-        <v>66</v>
-      </c>
-      <c r="BP1" t="s">
-        <v>67</v>
-      </c>
-      <c r="BQ1" t="s">
-        <v>68</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>69</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>70</v>
-      </c>
-      <c r="BT1" t="s">
-        <v>71</v>
-      </c>
-      <c r="BU1" t="s">
-        <v>72</v>
-      </c>
-      <c r="BV1" t="s">
-        <v>73</v>
-      </c>
-      <c r="BW1" t="s">
-        <v>74</v>
-      </c>
-      <c r="BX1" t="s">
-        <v>75</v>
-      </c>
-      <c r="BY1" t="s">
-        <v>76</v>
-      </c>
-      <c r="BZ1" t="s">
-        <v>77</v>
-      </c>
-      <c r="CA1" t="s">
-        <v>78</v>
-      </c>
-      <c r="CB1" t="s">
-        <v>79</v>
-      </c>
-      <c r="CC1" t="s">
-        <v>80</v>
-      </c>
-      <c r="CD1" t="s">
-        <v>81</v>
-      </c>
-      <c r="CE1" t="s">
-        <v>82</v>
-      </c>
-      <c r="CF1" t="s">
-        <v>83</v>
-      </c>
-      <c r="CG1" t="s">
-        <v>84</v>
-      </c>
-      <c r="CH1" t="s">
-        <v>85</v>
-      </c>
-      <c r="CI1" t="s">
-        <v>86</v>
-      </c>
-      <c r="CJ1" t="s">
-        <v>87</v>
-      </c>
-      <c r="CK1" t="s">
-        <v>88</v>
-      </c>
-      <c r="CL1" t="s">
-        <v>89</v>
-      </c>
-      <c r="CM1" t="s">
-        <v>90</v>
-      </c>
-      <c r="CN1" t="s">
-        <v>91</v>
-      </c>
-      <c r="CO1" t="s">
-        <v>92</v>
-      </c>
-      <c r="CP1" t="s">
-        <v>93</v>
-      </c>
-      <c r="CQ1" t="s">
-        <v>94</v>
-      </c>
-      <c r="CR1" t="s">
-        <v>95</v>
-      </c>
-      <c r="CS1" t="s">
-        <v>96</v>
-      </c>
-      <c r="CT1" t="s">
-        <v>97</v>
-      </c>
-      <c r="CU1" t="s">
-        <v>98</v>
-      </c>
-      <c r="CV1" t="s">
-        <v>99</v>
-      </c>
-      <c r="CW1" t="s">
-        <v>100</v>
-      </c>
-      <c r="CX1" t="s">
-        <v>101</v>
-      </c>
-      <c r="CY1" t="s">
-        <v>102</v>
-      </c>
-      <c r="CZ1" t="s">
-        <v>103</v>
-      </c>
-      <c r="DA1" t="s">
-        <v>104</v>
-      </c>
-      <c r="DB1" t="s">
-        <v>105</v>
-      </c>
-      <c r="DC1" t="s">
-        <v>106</v>
-      </c>
-      <c r="DD1" t="s">
-        <v>107</v>
-      </c>
-      <c r="DE1" t="s">
-        <v>108</v>
-      </c>
-      <c r="DF1" t="s">
-        <v>109</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nama Provinsi</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Nama Kabupaten Kota</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Nama Kecamatan</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Nama Faskes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Jumlah Peserta Hadir Usia 18 Tahun</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Jumlah Orang Diperiksa Tekanan Darah</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Jumlah Penderita Hipertensi</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Diagnosis Hipertensi</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Diagnosis Hipertensi - Gejala Masih Belum Spesifik</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Diagnosis Hipertensi - Keterbatasan Fasilitas Pemeriksaan</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Diagnosis Hipertensi - Waktu Pemeriksaan Terbatas</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Diagnosis Hipertensi - Perlu Rujukan ke Fasilitas yang Lebih Lengkap</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Diagnosis Hipertensi - Perlu Pemeriksaan Penunjang Lainnya</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Diagnosis Hipertensi - Lainnya</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Diberikan Obat</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Hipertensi - Obat Tidak Tersedia</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Hipertensi - Pasien Menolak Diberikan Obat</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Hipertensi - Riwayat Alergi atau Kontraindikasi Obat</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Hipertensi - Tidak Ada Indikasi Medis</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Hipertensi - Risiko Efek Samping Lebih Besar Daripada Manfaat</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Hipertensi - Tidak Masuk dalam Skema Pembiayaan Puskesmas</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Hipertensi - Lainnya</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Edukasi Hipertensi</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Rujuk Hipertensi</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Rujuk Hipertensi Derajat 3</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Jumlah Peserta hadir Usia ≥18 Tahun</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Jumlah Orang Diperiksa gula darah (Usia ≥ 18 Tahun)</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Jumlah Penderita Diabetes</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Diberikan Diagnosis</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Diagnosis Diabetes - Gejala Masih Belum Spesifik</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Diagnosis Diabetes - Keterbatasan Fasilitas Pemeriksaan</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Diagnosis Diabetes - Waktu Pemeriksaan Terbatas</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Diagnosis Diabetes - Perlu Rujukan ke Fasilitas yang Lebih Lengkap</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Diagnosis Diabetes - Perlu Pemeriksaan Penunjang Lainnya</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Diagnosis Diabetes - Lainnya</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Diberikan Obat Diabetes</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Diabetes - Obat Tidak Tersedia</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Diabetes - Pasien Menolak Diberikan Obat</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Diabetes - Riwayat Alergi Atau Kontraindikasi Obat</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Diabetes - Tidak Ada Indikasi Medis</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Diabetes - Risiko Efek Samping Lebih Besar Daripada Manfaat</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Diabetes - Tidak Masuk Dalam Skema Pembiayaan Puskesmas</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Diabetes - Lainnya</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>Edukasi Diabetes</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>Rujuk Diabetes</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>Jumlah Penderita Prediabetes ≥18 Tahun</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>Jumlah Penderita Prediabetes risiko tinggi* ≥18 Tahun</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>Jumlah Penderita Prediabetes risiko tinggi* yang didiagnosis</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Diagnosis Prediabetes - Gejala Masih Belum Spesifik</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Diagnosis Prediabetes - Keterbatasan Fasilitas Pemeriksaan</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Diagnosis Prediabetes - Waktu Pemeriksaan Terbatas</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Diagnosis Prediabetes - Perlu Rujukan ke Fasilitas yang Lebih Lengkap</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Diagnosis Prediabetes - Perlu Pemeriksaan Penunjang Lainnya</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Diagnosis Prediabetes - Lainnya</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>Jumlah Penderita Prediabetes risiko tinggi* yang diberikan Obat</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Prediabetes - Obat Tidak Tersedia</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Prediabetes - Pasien Menolak Diberikan Obat</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Prediabetes - Riwayat Alergi Atau Kontraindikasi Obat</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Prediabetes - Tidak Ada Indikasi Medis</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Prediabetes - Risiko Efek Samping Lebih Besar Daripada Manfaat</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Prediabetes - Tidak Masuk Dalam Skema Pembiayaan Puskesmas</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Prediabetes - Lainnya</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>Edukasi Prediabetes (semua)</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>Rujuk Prediabetes (semua)</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>Jumlah Peserta Usia 40 Tahun dengan  HT dan/atau DM</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>Jumlah Peserta Usia 40 Tahun dengan  HT dan/atau DM yang Diperiksa profil lipid</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>Jumlah Peserta Dislipidemia</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>Diagnosis Dislipidemia</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Diagnosis - Gejala Masih Belum Spesifik</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Diagnosis - Keterbatasan Fasilitas Pemeriksaan</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Diagnosis - Waktu Pemeriksaan Terbatas</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Diagnosis - Perlu Rujukan Ke Fasilitas Yang Lebih Lengkap</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Diagnosis - Perlu Pemeriksaan Penunjang Lainnya</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Diagnosis - Lainnya</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>Diberikan Obat dislipidemia</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Dislipidemia - Obat Tidak Tersedia</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Dislipidemia - Pasien Menolak Diberikan Obat</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Dislipidemia - Riwayat Alergi Atau Kontraindikasi Obat</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Dislipidemia - Tidak Ada Indikasi Medis</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Dislipidemia - Risiko Efek Samping Lebih Besar Daripada Manfaat</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Dislipidemia - Tidak Masuk Dalam Skema Pembiayaan Puskesmas</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>Alasan Tidak Diberikan Obat Dislipidemia - Lainnya</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>Edukasi Dislipidemia</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>Total Peserta hadir (semua umur)</t>
+        </is>
+      </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>Total Peserta Diperiksa karies gigi</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
+        <is>
+          <t>Jumlah Peserta dengan Gigi Karies (semua umur =&gt;1 Tahun)</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>Tertatalaksana Gigi Karies (semua umur =&gt;1 Tahun)</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
+          <t>Diagnosis Gigi Karies (semua umur =&gt;1 Tahun)</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>Tindakan Medis Gigi Karies (semua umur =&gt;1 Tahun)</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
+          <t>Obat Gigi Karies (semua umur =&gt;1 Tahun)</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>Tindak Lanjut Gigi Karies (semua umur =&gt;1 Tahun)</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>Edukasi Gigi Karies (semua umur =&gt;1 Tahun)</t>
+        </is>
+      </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>Diagnosis dan Edukasi Gigi Karies (semua umur =&gt;1 Tahun)</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>Diagnosis Edukasi dan Tindakan Medis Gigi Karies (semua umur =&gt;1 Tahun)</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>Diagnosis Edukasi dan Obat Gigi Karies (semua umur =&gt;1 Tahun)</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>Diagnosis dan Edukasi dan Obat dan Tindakan Medis Gigi Karies (semua umur =&gt;1 Tahun)</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>Jumlah Peserta hadir Usia 6-12 Tahun</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>Total Peserta Diperiksa Gigi Karies (Usia 6-12 Tahun)</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>Jumlah Peserta tanpa Gigi Karies (Usia 6-12 Tahun)</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>Jumlah Peserta dengan Gigi Karies (Usia 6-12 Tahun)</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>Tertatalaksana Gigi Karies (Usia 6-12 Tahun)</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>Diagnosis Gigi Karies (Usia 6-12 Tahun)</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>Tindakan medis Gigi Karies (Usia 6-12 Tahun)</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>Tindakan medis 'pemberian fluoride' Gigi Karies (Usia 6-12 Tahun)</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>Edukasi Gigi Karies (Usia 6-12 Tahun)</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>Diberikan Obat Gigi Karies (Usia 6-12 Tahun)</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>Diagnosis dan Edukasi Gigi Karies (Usia 6-12 Tahun)</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>Diagnosis dan Edukasi dan Tindakan Medis Gigi Karies (Usia 6-12 Tahun)</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>Diagnosis dan Edukasi dan Obat Gigi Karies (Usia 6-12 Tahun)</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>Diagnosis dan Edukasi dan Obat dan Tindakan Medis Gigi Karies (Usia 6-12 Tahun)</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:110" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D2" t="s">
-        <v>113</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kab. Pangkajene Kepulauan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Balocci</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BALOCCI</t>
+        </is>
       </c>
       <c r="E2">
         <v>1427</v>
@@ -1437,18 +1207,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:110" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D3" t="s">
-        <v>115</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kab. Pangkajene Kepulauan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Tondong Tallasa</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>BANTIMALA</t>
+        </is>
       </c>
       <c r="E3">
         <v>7071</v>
@@ -1769,18 +1547,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:110" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D4" t="s">
-        <v>117</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kab. Pangkajene Kepulauan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Segeri</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>BARING</t>
+        </is>
       </c>
       <c r="E4">
         <v>4783</v>
@@ -2101,18 +1887,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:110" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>110</v>
-      </c>
-      <c r="B5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D5" t="s">
-        <v>119</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kab. Pangkajene Kepulauan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Pangkajene</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>BONTO PERAK</t>
+        </is>
       </c>
       <c r="E5">
         <v>13154</v>
@@ -2433,18 +2227,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:110" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>110</v>
-      </c>
-      <c r="B6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" t="s">
-        <v>120</v>
-      </c>
-      <c r="D6" t="s">
-        <v>121</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kab. Pangkajene Kepulauan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bungoro</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>BOWONG CINDEA</t>
+        </is>
       </c>
       <c r="E6">
         <v>9787</v>
@@ -2765,18 +2567,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:110" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>110</v>
-      </c>
-      <c r="B7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C7" t="s">
-        <v>120</v>
-      </c>
-      <c r="D7" t="s">
-        <v>122</v>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kab. Pangkajene Kepulauan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bungoro</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BUNGORO</t>
+        </is>
       </c>
       <c r="E7">
         <v>19342</v>
@@ -3097,18 +2907,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:110" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>110</v>
-      </c>
-      <c r="B8" t="s">
-        <v>111</v>
-      </c>
-      <c r="C8" t="s">
-        <v>123</v>
-      </c>
-      <c r="D8" t="s">
-        <v>124</v>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kab. Pangkajene Kepulauan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Minasate'ne</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>KALABBIRANG</t>
+        </is>
       </c>
       <c r="E8">
         <v>5410</v>
@@ -3429,18 +3247,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:110" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B9" t="s">
-        <v>111</v>
-      </c>
-      <c r="C9" t="s">
-        <v>118</v>
-      </c>
-      <c r="D9" t="s">
-        <v>125</v>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kab. Pangkajene Kepulauan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Pangkajene</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>KOTA PANGKAJENE</t>
+        </is>
       </c>
       <c r="E9">
         <v>21299</v>
@@ -3761,18 +3587,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:110" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>110</v>
-      </c>
-      <c r="B10" t="s">
-        <v>111</v>
-      </c>
-      <c r="C10" t="s">
-        <v>126</v>
-      </c>
-      <c r="D10" t="s">
-        <v>127</v>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kab. Pangkajene Kepulauan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Labakkang</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LABAKKANG</t>
+        </is>
       </c>
       <c r="E10">
         <v>11021</v>
@@ -4093,18 +3927,26 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:110" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>110</v>
-      </c>
-      <c r="B11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C11" t="s">
-        <v>128</v>
-      </c>
-      <c r="D11" t="s">
-        <v>129</v>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kab. Pangkajene Kepulauan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Liukang Kalmas</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LIUKANG KALMAS</t>
+        </is>
       </c>
       <c r="E11">
         <v>2837</v>
@@ -4425,18 +4267,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:110" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>110</v>
-      </c>
-      <c r="B12" t="s">
-        <v>111</v>
-      </c>
-      <c r="C12" t="s">
-        <v>130</v>
-      </c>
-      <c r="D12" t="s">
-        <v>131</v>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kab. Pangkajene Kepulauan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Liukang Tangaya</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LIUKANG TANGAYA</t>
+        </is>
       </c>
       <c r="E12">
         <v>6783</v>
@@ -4757,18 +4607,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:110" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C13" t="s">
-        <v>132</v>
-      </c>
-      <c r="D13" t="s">
-        <v>133</v>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kab. Pangkajene Kepulauan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Liukang Tupabbiring</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LIUKANG TUPABBIRING</t>
+        </is>
       </c>
       <c r="E13">
         <v>4095</v>
@@ -5089,18 +4947,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:110" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>110</v>
-      </c>
-      <c r="B14" t="s">
-        <v>111</v>
-      </c>
-      <c r="C14" t="s">
-        <v>134</v>
-      </c>
-      <c r="D14" t="s">
-        <v>135</v>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kab. Pangkajene Kepulauan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Mandalle</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>MANDALLE</t>
+        </is>
       </c>
       <c r="E14">
         <v>9232</v>
@@ -5421,18 +5287,26 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:110" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>110</v>
-      </c>
-      <c r="B15" t="s">
-        <v>111</v>
-      </c>
-      <c r="C15" t="s">
-        <v>136</v>
-      </c>
-      <c r="D15" t="s">
-        <v>137</v>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kab. Pangkajene Kepulauan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Marang</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MA'RANG</t>
+        </is>
       </c>
       <c r="E15">
         <v>17978</v>
@@ -5753,18 +5627,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:110" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>110</v>
-      </c>
-      <c r="B16" t="s">
-        <v>111</v>
-      </c>
-      <c r="C16" t="s">
-        <v>123</v>
-      </c>
-      <c r="D16" t="s">
-        <v>138</v>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kab. Pangkajene Kepulauan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Minasate'ne</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MINASATE'NE</t>
+        </is>
       </c>
       <c r="E16">
         <v>13145</v>
@@ -6085,18 +5967,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:110" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>110</v>
-      </c>
-      <c r="B17" t="s">
-        <v>111</v>
-      </c>
-      <c r="C17" t="s">
-        <v>136</v>
-      </c>
-      <c r="D17" t="s">
-        <v>139</v>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kab. Pangkajene Kepulauan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Marang</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PADANG LAMPE</t>
+        </is>
       </c>
       <c r="E17">
         <v>6001</v>
@@ -6417,18 +6307,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:110" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>110</v>
-      </c>
-      <c r="B18" t="s">
-        <v>111</v>
-      </c>
-      <c r="C18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D18" t="s">
-        <v>140</v>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kab. Pangkajene Kepulauan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Liukang Kalmas</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PAMMANTAUANG</t>
+        </is>
       </c>
       <c r="E18">
         <v>3502</v>
@@ -6749,18 +6647,26 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:110" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>110</v>
-      </c>
-      <c r="B19" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D19" t="s">
-        <v>141</v>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kab. Pangkajene Kepulauan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Labakkang</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PUNDATA BAJI</t>
+        </is>
       </c>
       <c r="E19">
         <v>9703</v>
@@ -7081,18 +6987,26 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:110" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>110</v>
-      </c>
-      <c r="B20" t="s">
-        <v>111</v>
-      </c>
-      <c r="C20" t="s">
-        <v>142</v>
-      </c>
-      <c r="D20" t="s">
-        <v>143</v>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kab. Pangkajene Kepulauan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Liukang Tupabbiring Utara</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SABUTUNG</t>
+        </is>
       </c>
       <c r="E20">
         <v>8451</v>
@@ -7413,18 +7327,26 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:110" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>110</v>
-      </c>
-      <c r="B21" t="s">
-        <v>111</v>
-      </c>
-      <c r="C21" t="s">
-        <v>130</v>
-      </c>
-      <c r="D21" t="s">
-        <v>144</v>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kab. Pangkajene Kepulauan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Liukang Tangaya</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SAILUS</t>
+        </is>
       </c>
       <c r="E21">
         <v>4401</v>
@@ -7745,18 +7667,26 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:110" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>110</v>
-      </c>
-      <c r="B22" t="s">
-        <v>111</v>
-      </c>
-      <c r="C22" t="s">
-        <v>132</v>
-      </c>
-      <c r="D22" t="s">
-        <v>145</v>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kab. Pangkajene Kepulauan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Liukang Tupabbiring</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SARAPPO</t>
+        </is>
       </c>
       <c r="E22">
         <v>7323</v>
@@ -8077,18 +8007,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:110" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>110</v>
-      </c>
-      <c r="B23" t="s">
-        <v>111</v>
-      </c>
-      <c r="C23" t="s">
-        <v>116</v>
-      </c>
-      <c r="D23" t="s">
-        <v>146</v>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kab. Pangkajene Kepulauan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Segeri</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SEGERI</t>
+        </is>
       </c>
       <c r="E23">
         <v>10243</v>
@@ -8409,18 +8347,26 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:110" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>110</v>
-      </c>
-      <c r="B24" t="s">
-        <v>111</v>
-      </c>
-      <c r="C24" t="s">
-        <v>126</v>
-      </c>
-      <c r="D24" t="s">
-        <v>147</v>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kab. Pangkajene Kepulauan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Labakkang</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TARAWEANG</t>
+        </is>
       </c>
       <c r="E24">
         <v>8832</v>
@@ -8742,6 +8688,5 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data_default.xlsx
+++ b/data_default.xlsx
@@ -5489,7 +5489,7 @@
         <v>255</v>
       </c>
       <c r="BM15">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="BN15">
         <v>1</v>
@@ -7965,19 +7965,19 @@
         <v>13</v>
       </c>
       <c r="CS22">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="CT22">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="CU22">
         <v>296</v>
       </c>
       <c r="CV22">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="CW22">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="CX22">
         <v>703</v>
@@ -7989,7 +7989,7 @@
         <v>0</v>
       </c>
       <c r="DA22">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="DB22">
         <v>2</v>

--- a/data_default.xlsx
+++ b/data_default.xlsx
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="E9">
-        <v>21299</v>
+        <v>21300</v>
       </c>
       <c r="F9">
-        <v>20962</v>
+        <v>20963</v>
       </c>
       <c r="G9">
         <v>1118</v>
@@ -3332,10 +3332,10 @@
         <v>99</v>
       </c>
       <c r="Z9">
-        <v>21299</v>
+        <v>21300</v>
       </c>
       <c r="AA9">
-        <v>19162</v>
+        <v>19163</v>
       </c>
       <c r="AB9">
         <v>349</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="CS12">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="CT12">
         <v>2042</v>
@@ -5489,7 +5489,7 @@
         <v>255</v>
       </c>
       <c r="BM15">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="BN15">
         <v>1</v>
@@ -5829,7 +5829,7 @@
         <v>29</v>
       </c>
       <c r="BM16">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="BN16">
         <v>3</v>
@@ -7965,19 +7965,19 @@
         <v>13</v>
       </c>
       <c r="CS22">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="CT22">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="CU22">
         <v>296</v>
       </c>
       <c r="CV22">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="CW22">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="CX22">
         <v>703</v>
@@ -7989,7 +7989,7 @@
         <v>0</v>
       </c>
       <c r="DA22">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="DB22">
         <v>2</v>
